--- a/public/download/testallcriteria2.xlsx
+++ b/public/download/testallcriteria2.xlsx
@@ -479,7 +479,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -516,12 +516,6 @@
       <name val="Noto Sans Devanagari"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -582,7 +576,7 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -608,7 +602,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L1048576"/>
-  <sheetFormatPr defaultColWidth="8.609375" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6171875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="44.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="47.17"/>
@@ -703,19 +697,19 @@
         <v>13</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G3" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H3" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" s="0" t="s">
         <v>14</v>

--- a/public/download/testallcriteria2.xlsx
+++ b/public/download/testallcriteria2.xlsx
@@ -604,7 +604,7 @@
   <dimension ref="A1:L1048576"/>
   <sheetFormatPr defaultColWidth="8.6171875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="44.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="133.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="47.17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="19.18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15.54"/>
